--- a/data/trans_dic/IP2905_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna</t>
+          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,75; 75,38</t>
+          <t>44,68; 75,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,52; 55,51</t>
+          <t>32,28; 56,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,58; 61,98</t>
+          <t>42,11; 62,57</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,39; 50,22</t>
+          <t>41,84; 50,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,12; 53,59</t>
+          <t>44,05; 54,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,23; 51,3</t>
+          <t>44,27; 50,97</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50,02; 63,35</t>
+          <t>49,91; 63,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,39; 66,12</t>
+          <t>52,91; 66,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,32; 63,0</t>
+          <t>53,65; 63,48</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,27; 53,41</t>
+          <t>46,05; 53,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,13; 54,86</t>
+          <t>47,06; 54,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,75; 52,88</t>
+          <t>47,76; 53,0</t>
         </is>
       </c>
     </row>
@@ -752,4 +753,380 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>32295</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25401</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>57696</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>23995; 40596</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18836; 32748</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>47184; 70107</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>193509</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>244096</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>437605</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>175709; 213111</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221178; 271357</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>408130; 469984</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>81269</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>106585</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>187853</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>71644; 90834</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>94514; 117924</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>172851; 204500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>307072</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>376082</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>683154</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>284215; 328451</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>347770; 404953</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>647670; 718829</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2905_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>44,68; 75,6</t>
+          <t>45,14; 73,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,28; 56,13</t>
+          <t>31,72; 55,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,11; 62,57</t>
+          <t>42,73; 62,36</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,84; 50,75</t>
+          <t>41,87; 50,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,05; 54,05</t>
+          <t>44,14; 54,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,27; 50,97</t>
+          <t>44,03; 50,78</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,91; 63,29</t>
+          <t>49,85; 63,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,91; 66,02</t>
+          <t>52,86; 66,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,65; 63,48</t>
+          <t>53,04; 62,97</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,05; 53,22</t>
+          <t>46,25; 53,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,06; 54,79</t>
+          <t>47,2; 54,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,76; 53,0</t>
+          <t>47,89; 53,07</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23995; 40596</t>
+          <t>24240; 39662</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18836; 32748</t>
+          <t>18505; 32393</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47184; 70107</t>
+          <t>47872; 69866</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>175709; 213111</t>
+          <t>175800; 211395</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>221178; 271357</t>
+          <t>221620; 271558</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>408130; 469984</t>
+          <t>405928; 468201</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>71644; 90834</t>
+          <t>71549; 90664</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94514; 117924</t>
+          <t>94415; 118296</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>172851; 204500</t>
+          <t>170887; 202862</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>284215; 328451</t>
+          <t>285420; 329485</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>347770; 404953</t>
+          <t>348861; 404445</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>647670; 718829</t>
+          <t>649453; 719706</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2905_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>49,39%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,14; 73,86</t>
+          <t>29,68; 53,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,72; 55,52</t>
+          <t>46,32; 71,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,73; 62,36</t>
+          <t>40,61; 58,21</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,06%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>41,87; 50,34</t>
+          <t>43,96; 53,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,14; 54,09</t>
+          <t>41,82; 49,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44,03; 50,78</t>
+          <t>43,93; 50,52</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,05%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,85; 63,17</t>
+          <t>52,58; 65,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52,86; 66,22</t>
+          <t>50,36; 63,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53,04; 62,97</t>
+          <t>52,84; 62,65</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,88%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>46,25; 53,39</t>
+          <t>46,79; 54,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>47,2; 54,73</t>
+          <t>46,15; 52,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47,89; 53,07</t>
+          <t>47,44; 52,29</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32295</t>
+          <t>22233</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25401</t>
+          <t>26970</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57696</t>
+          <t>49202</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24240; 39662</t>
+          <t>15941; 28884</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18505; 32393</t>
+          <t>21264; 32792</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47872; 69866</t>
+          <t>40454; 57987</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>287</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>193509</t>
+          <t>224132</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>244096</t>
+          <t>189734</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>437605</t>
+          <t>413867</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>175800; 211395</t>
+          <t>203706; 246423</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>221620; 271558</t>
+          <t>173977; 207000</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>405928; 468201</t>
+          <t>386336; 444295</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>124</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81269</t>
+          <t>96729</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>106585</t>
+          <t>82447</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>187853</t>
+          <t>179176</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>71549; 90664</t>
+          <t>86364; 107924</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94415; 118296</t>
+          <t>72706; 91676</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>170887; 202862</t>
+          <t>163092; 193371</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>448</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>307072</t>
+          <t>343094</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>376082</t>
+          <t>299151</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>683154</t>
+          <t>642245</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>285420; 329485</t>
+          <t>318777; 369021</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>348861; 404445</t>
+          <t>279774; 321101</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>649453; 719706</t>
+          <t>610910; 673305</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2905_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP2905_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>41,39%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>58,75%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>49,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>29,68; 53,77</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>46,32; 71,43</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>40,61; 58,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>48,37%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>45,61%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>47,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>43,96; 53,18</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>41,82; 49,76</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>43,93; 50,52</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>58,89%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>57,11%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>58,05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>52,58; 65,7</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>50,36; 63,5</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>52,84; 62,65</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>50,36%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>49,34%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>49,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>46,79; 54,16</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>46,15; 52,96</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>47,44; 52,29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.4139006005043965</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5875089609448586</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.4938995306896569</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>22233</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>26970</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49202</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.2967645870225042</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.4632120983151634</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.406087982401811</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>15941; 28884</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>21264; 32792</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>40454; 57987</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.5377181822300202</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7143394657239899</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.5820815697450031</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.4837112894942011</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.4560835199383528</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4706412605776191</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>224132</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>189734</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>413867</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4396275363712491</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.4182067548521424</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.4393331868216503</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>203706; 246423</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>173977; 207000</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>386336; 444295</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.5318165478079282</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.4975857894743693</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.5052437835509642</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.5888578071469652</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5710909831024796</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.5805471203456896</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>96729</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>82447</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>179176</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.5257555700596199</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.5036128463360617</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.5284323406658558</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>86364; 107924</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>72706; 91676</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>163092; 193371</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.657004761983344</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.6350178537954778</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6265416565987032</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.5035575957947974</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4934200766445111</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.4987843142767456</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>343094</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>299151</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>642245</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.4678663240910743</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.4614603420170022</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.4744489337927967</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>318777; 369021</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>279774; 321101</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>610910; 673305</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.5416091898780893</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.5296243182467751</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.5229064854850568</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que durante sus primeros meses de vida solo recibieron lactancia materna (tasa de respuesta: 98,87%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>22233</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>26970</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>49202</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>15941</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>21264</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>40454</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>28884</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>32792</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>57987</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>308</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>287</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>224132</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>189734</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>413867</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>203706</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>173977</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>386336</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>246423</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>207000</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>444295</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>96729</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>82447</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>179176</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>86364</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>72706</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>163092</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>107924</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>91676</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>193371</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>475</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>448</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>343094</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>299151</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>642245</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>318777</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>279774</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>610910</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>369021</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>321101</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>673305</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>